--- a/data/Appendix A.xlsx
+++ b/data/Appendix A.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/53aff1208ed7b64f/Post-doc/floating_solar/final submission/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\allis\OneDrive\Post-doc\floating_solar\floating_solar\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="8_{049DD433-D6FC-4140-A877-FC39B2E6DFCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F9F17AF-4446-4AC2-83E4-E5DAC7E3F441}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{909556B8-C4BD-4155-9756-E34765EFFD91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{8DC43449-862C-4354-9E64-06AF07CFDE3F}"/>
+    <workbookView xWindow="38290" yWindow="1720" windowWidth="25820" windowHeight="15500" xr2:uid="{8DC43449-862C-4354-9E64-06AF07CFDE3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Table S1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1860" uniqueCount="1005">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1863" uniqueCount="1007">
   <si>
     <t>species_code</t>
   </si>
@@ -3036,6 +3036,12 @@
   </si>
   <si>
     <t>Vulnerability Index, calculated using habitat_score, CCS_quantile, wingloading_quantile, and vis_acuity_risk, and the equation described in Figure 1 of the main text.</t>
+  </si>
+  <si>
+    <t>VI_scaled</t>
+  </si>
+  <si>
+    <t>VI values scaled between 0 and 1.</t>
   </si>
 </sst>
 </file>
@@ -3519,9 +3525,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3897,13 +3904,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F4480A-BF10-4438-8F3C-B4F102775CEB}">
-  <dimension ref="A1:S292"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:T292"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -3958,8 +3965,11 @@
       <c r="S1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T1" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4014,8 +4024,11 @@
       <c r="S2">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T2">
+        <v>4.8582995951416998E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4070,8 +4083,11 @@
       <c r="S3">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T3">
+        <v>3.6437246963562701E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4126,8 +4142,11 @@
       <c r="S4">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T4">
+        <v>8.5020242914979699E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4182,8 +4201,11 @@
       <c r="S5">
         <v>65</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T5">
+        <v>0.51417004048582904</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4241,8 +4263,11 @@
       <c r="S6">
         <v>87.5</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T6">
+        <v>0.69635627530364297</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4297,8 +4322,11 @@
       <c r="S7">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T7">
+        <v>1.6194331983805599E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4353,8 +4381,11 @@
       <c r="S8">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T8">
+        <v>8.0971659919028306E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4409,8 +4440,11 @@
       <c r="S9">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T9">
+        <v>4.8582995951416998E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4468,8 +4502,11 @@
       <c r="S10">
         <v>14.666666666999999</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T10">
+        <v>0.106612685562753</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4524,8 +4561,11 @@
       <c r="S11">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T11">
+        <v>2.0242914979756998E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4580,8 +4620,11 @@
       <c r="S12">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T12">
+        <v>1.2145748987854201E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4636,8 +4679,11 @@
       <c r="S13">
         <v>28</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T13">
+        <v>0.21457489878542499</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4695,8 +4741,11 @@
       <c r="S14">
         <v>77.777777775000004</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T14">
+        <v>0.617633828137651</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4751,8 +4800,11 @@
       <c r="S15">
         <v>6</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T15">
+        <v>3.6437246963562701E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4810,8 +4862,11 @@
       <c r="S16">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T16">
+        <v>1.6194331983805599E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4866,8 +4921,11 @@
       <c r="S17">
         <v>8.2058823524999998</v>
       </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T17">
+        <v>5.4298642530364302E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4925,8 +4983,11 @@
       <c r="S18">
         <v>106.696428575</v>
       </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T18">
+        <v>0.85179294392712501</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4981,8 +5042,11 @@
       <c r="S19">
         <v>29.7</v>
       </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T19">
+        <v>0.228340080971659</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -5037,8 +5101,11 @@
       <c r="S20">
         <v>16</v>
       </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T20">
+        <v>0.11740890688259099</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -5096,8 +5163,11 @@
       <c r="S21">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T21">
+        <v>0.11740890688259099</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -5155,8 +5225,11 @@
       <c r="S22">
         <v>12</v>
       </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T22">
+        <v>8.5020242914979699E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -5211,8 +5284,11 @@
       <c r="S23">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T23">
+        <v>2.0242914979756998E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -5267,8 +5343,11 @@
       <c r="S24">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T24">
+        <v>2.0242914979756998E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -5323,8 +5402,11 @@
       <c r="S25">
         <v>54</v>
       </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T25">
+        <v>0.42510121457489802</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -5379,8 +5461,11 @@
       <c r="S26">
         <v>31.5</v>
       </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T26">
+        <v>0.24291497975708501</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5435,8 +5520,11 @@
       <c r="S27">
         <v>19.107142857500001</v>
       </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T27">
+        <v>0.14256795836032299</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5491,8 +5579,11 @@
       <c r="S28">
         <v>14</v>
       </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T28">
+        <v>0.10121457489878501</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5550,8 +5641,11 @@
       <c r="S29">
         <v>75</v>
       </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T29">
+        <v>0.59514170040485803</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5606,8 +5700,11 @@
       <c r="S30">
         <v>9.7058823524999998</v>
       </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T30">
+        <v>6.6444391518218598E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5662,8 +5759,11 @@
       <c r="S31">
         <v>3.4545454549999999</v>
       </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T31">
+        <v>1.58262789878542E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5718,8 +5818,11 @@
       <c r="S32">
         <v>2</v>
       </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T32">
+        <v>4.0485829959514101E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5774,8 +5877,11 @@
       <c r="S33">
         <v>10</v>
       </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T33">
+        <v>6.8825910931174003E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5830,8 +5936,11 @@
       <c r="S34">
         <v>64</v>
       </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T34">
+        <v>0.50607287449392702</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5886,8 +5995,11 @@
       <c r="S35">
         <v>27</v>
       </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T35">
+        <v>0.206477732793522</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5942,8 +6054,11 @@
       <c r="S36">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T36">
+        <v>1.2145748987854201E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5998,8 +6113,11 @@
       <c r="S37">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T37">
+        <v>1.6194331983805599E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -6054,8 +6172,11 @@
       <c r="S38">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T38">
+        <v>8.0971659919028306E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -6110,8 +6231,11 @@
       <c r="S39">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T39">
+        <v>1.6194331983805599E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -6166,8 +6290,11 @@
       <c r="S40">
         <v>15</v>
       </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T40">
+        <v>0.109311740890688</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -6222,8 +6349,11 @@
       <c r="S41">
         <v>17.5</v>
       </c>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T41">
+        <v>0.12955465587044501</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -6278,8 +6408,11 @@
       <c r="S42">
         <v>12</v>
       </c>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T42">
+        <v>8.5020242914979699E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -6337,8 +6470,11 @@
       <c r="S43">
         <v>12</v>
       </c>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T43">
+        <v>8.5020242914979699E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -6393,8 +6529,11 @@
       <c r="S44">
         <v>20</v>
       </c>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T44">
+        <v>0.14979757085020201</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -6449,8 +6588,11 @@
       <c r="S45">
         <v>21</v>
       </c>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T45">
+        <v>0.157894736842105</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -6505,8 +6647,11 @@
       <c r="S46">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T46">
+        <v>8.0971659919028306E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -6561,8 +6706,11 @@
       <c r="S47">
         <v>6</v>
       </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T47">
+        <v>3.6437246963562701E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -6617,8 +6765,11 @@
       <c r="S48">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T48">
+        <v>2.0242914979756998E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -6673,8 +6824,11 @@
       <c r="S49">
         <v>24</v>
       </c>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T49">
+        <v>0.18218623481781299</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -6729,8 +6883,11 @@
       <c r="S50">
         <v>14</v>
       </c>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T50">
+        <v>0.10121457489878501</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -6785,8 +6942,11 @@
       <c r="S51">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T51">
+        <v>8.0971659919028306E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
@@ -6841,8 +7001,11 @@
       <c r="S52">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T52">
+        <v>4.8582995951416998E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
@@ -6897,8 +7060,11 @@
       <c r="S53">
         <v>10</v>
       </c>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T53">
+        <v>6.8825910931174003E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
@@ -6956,8 +7122,11 @@
       <c r="S54">
         <v>94.196428574999999</v>
       </c>
-    </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T54">
+        <v>0.75057836902833996</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -7012,8 +7181,11 @@
       <c r="S55">
         <v>32</v>
       </c>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T55">
+        <v>0.24696356275303599</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
@@ -7068,8 +7240,11 @@
       <c r="S56">
         <v>4</v>
       </c>
-    </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T56">
+        <v>2.0242914979756998E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -7124,8 +7299,11 @@
       <c r="S57">
         <v>2</v>
       </c>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T57">
+        <v>4.0485829959514101E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
@@ -7180,8 +7358,11 @@
       <c r="S58">
         <v>14</v>
       </c>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T58">
+        <v>0.10121457489878501</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -7236,8 +7417,11 @@
       <c r="S59">
         <v>6.1764705874999999</v>
       </c>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T59">
+        <v>3.7866158603238803E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -7292,8 +7476,11 @@
       <c r="S60">
         <v>48</v>
       </c>
-    </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T60">
+        <v>0.376518218623481</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
@@ -7348,8 +7535,11 @@
       <c r="S61">
         <v>8</v>
       </c>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T61">
+        <v>5.2631578947368397E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
@@ -7404,8 +7594,11 @@
       <c r="S62">
         <v>54</v>
       </c>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T62">
+        <v>0.42510121457489802</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
@@ -7460,8 +7653,11 @@
       <c r="S63">
         <v>48</v>
       </c>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T63">
+        <v>0.376518218623481</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
@@ -7516,8 +7712,11 @@
       <c r="S64">
         <v>8.6764705875000008</v>
       </c>
-    </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T64">
+        <v>5.8109073582995899E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
@@ -7572,8 +7771,11 @@
       <c r="S65">
         <v>3.6666666659999998</v>
       </c>
-    </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T65">
+        <v>1.75438596437246E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
@@ -7628,8 +7830,11 @@
       <c r="S66">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T66">
+        <v>1.2145748987854201E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
@@ -7684,8 +7889,11 @@
       <c r="S67">
         <v>70</v>
       </c>
-    </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T67">
+        <v>0.55465587044534403</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
@@ -7740,8 +7948,11 @@
       <c r="S68">
         <v>14</v>
       </c>
-    </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T68">
+        <v>0.10121457489878501</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
@@ -7796,8 +8007,11 @@
       <c r="S69">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
@@ -7852,8 +8066,11 @@
       <c r="S70">
         <v>8.6764705875000008</v>
       </c>
-    </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T70">
+        <v>5.8109073582995899E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
@@ -7908,8 +8125,11 @@
       <c r="S71">
         <v>5</v>
       </c>
-    </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T71">
+        <v>2.8340080971659899E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
@@ -7964,8 +8184,11 @@
       <c r="S72">
         <v>12.5</v>
       </c>
-    </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T72">
+        <v>8.9068825910931099E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
@@ -8020,8 +8243,11 @@
       <c r="S73">
         <v>8</v>
       </c>
-    </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T73">
+        <v>5.2631578947368397E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
@@ -8076,8 +8302,11 @@
       <c r="S74">
         <v>8</v>
       </c>
-    </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T74">
+        <v>5.2631578947368397E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
@@ -8132,8 +8361,11 @@
       <c r="S75">
         <v>6.6250000005</v>
       </c>
-    </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T75">
+        <v>4.1497975712550601E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
@@ -8188,8 +8420,11 @@
       <c r="S76">
         <v>2.25</v>
       </c>
-    </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T76">
+        <v>6.0728744939271204E-3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
@@ -8244,8 +8479,11 @@
       <c r="S77">
         <v>36</v>
       </c>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T77">
+        <v>0.27935222672064702</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
@@ -8303,8 +8541,11 @@
       <c r="S78">
         <v>33</v>
       </c>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T78">
+        <v>0.25506072874493901</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
@@ -8359,8 +8600,11 @@
       <c r="S79">
         <v>9</v>
       </c>
-    </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T79">
+        <v>6.0728744939271197E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
@@ -8415,8 +8659,11 @@
       <c r="S80">
         <v>12</v>
       </c>
-    </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T80">
+        <v>8.5020242914979699E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
@@ -8471,8 +8718,11 @@
       <c r="S81">
         <v>28</v>
       </c>
-    </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T81">
+        <v>0.21457489878542499</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>81</v>
       </c>
@@ -8527,8 +8777,11 @@
       <c r="S82">
         <v>8</v>
       </c>
-    </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T82">
+        <v>5.2631578947368397E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>82</v>
       </c>
@@ -8583,8 +8836,11 @@
       <c r="S83">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T83">
+        <v>1.6194331983805599E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>83</v>
       </c>
@@ -8639,8 +8895,11 @@
       <c r="S84">
         <v>6.1875</v>
       </c>
-    </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T84">
+        <v>3.7955465587044497E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>84</v>
       </c>
@@ -8695,8 +8954,11 @@
       <c r="S85">
         <v>6</v>
       </c>
-    </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T85">
+        <v>3.6437246963562701E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>85</v>
       </c>
@@ -8751,8 +9013,11 @@
       <c r="S86">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T86">
+        <v>8.0971659919028306E-3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>86</v>
       </c>
@@ -8807,8 +9072,11 @@
       <c r="S87">
         <v>3</v>
       </c>
-    </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T87">
+        <v>1.2145748987854201E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>87</v>
       </c>
@@ -8863,8 +9131,11 @@
       <c r="S88">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T88">
+        <v>4.8582995951416998E-2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>88</v>
       </c>
@@ -8922,8 +9193,11 @@
       <c r="S89">
         <v>100</v>
       </c>
-    </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T89">
+        <v>0.79757085020242902</v>
+      </c>
+    </row>
+    <row r="90" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>89</v>
       </c>
@@ -8978,8 +9252,11 @@
       <c r="S90">
         <v>7</v>
       </c>
-    </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T90">
+        <v>4.4534412955465501E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>90</v>
       </c>
@@ -9037,8 +9314,11 @@
       <c r="S91">
         <v>50</v>
       </c>
-    </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T91">
+        <v>0.39271255060728699</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>91</v>
       </c>
@@ -9093,8 +9373,11 @@
       <c r="S92">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T92">
+        <v>8.0971659919028306E-3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>92</v>
       </c>
@@ -9149,8 +9432,11 @@
       <c r="S93">
         <v>20</v>
       </c>
-    </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T93">
+        <v>0.14979757085020201</v>
+      </c>
+    </row>
+    <row r="94" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>93</v>
       </c>
@@ -9205,8 +9491,11 @@
       <c r="S94">
         <v>14</v>
       </c>
-    </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T94">
+        <v>0.10121457489878501</v>
+      </c>
+    </row>
+    <row r="95" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>94</v>
       </c>
@@ -9261,8 +9550,11 @@
       <c r="S95">
         <v>13.5</v>
       </c>
-    </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T95">
+        <v>9.7165991902833995E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>95</v>
       </c>
@@ -9317,8 +9609,11 @@
       <c r="S96">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T96">
+        <v>1.2145748987854201E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>96</v>
       </c>
@@ -9373,8 +9668,11 @@
       <c r="S97">
         <v>10</v>
       </c>
-    </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T97">
+        <v>6.8825910931174003E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>97</v>
       </c>
@@ -9429,8 +9727,11 @@
       <c r="S98">
         <v>14.375</v>
       </c>
-    </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T98">
+        <v>0.104251012145748</v>
+      </c>
+    </row>
+    <row r="99" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>98</v>
       </c>
@@ -9485,8 +9786,11 @@
       <c r="S99">
         <v>9</v>
       </c>
-    </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T99">
+        <v>6.0728744939271197E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>99</v>
       </c>
@@ -9541,8 +9845,11 @@
       <c r="S100">
         <v>6</v>
       </c>
-    </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T100">
+        <v>3.6437246963562701E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>100</v>
       </c>
@@ -9597,8 +9904,11 @@
       <c r="S101">
         <v>12.8125</v>
       </c>
-    </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T101">
+        <v>9.15991902834008E-2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>101</v>
       </c>
@@ -9653,8 +9963,11 @@
       <c r="S102">
         <v>12.5</v>
       </c>
-    </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T102">
+        <v>8.9068825910931099E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>102</v>
       </c>
@@ -9709,8 +10022,11 @@
       <c r="S103">
         <v>10</v>
       </c>
-    </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T103">
+        <v>6.8825910931174003E-2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>103</v>
       </c>
@@ -9765,8 +10081,11 @@
       <c r="S104">
         <v>48</v>
       </c>
-    </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T104">
+        <v>0.376518218623481</v>
+      </c>
+    </row>
+    <row r="105" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>104</v>
       </c>
@@ -9821,8 +10140,11 @@
       <c r="S105">
         <v>4</v>
       </c>
-    </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T105">
+        <v>2.0242914979756998E-2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>105</v>
       </c>
@@ -9880,8 +10202,11 @@
       <c r="S106">
         <v>40</v>
       </c>
-    </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T106">
+        <v>0.311740890688259</v>
+      </c>
+    </row>
+    <row r="107" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>106</v>
       </c>
@@ -9939,8 +10264,11 @@
       <c r="S107">
         <v>45.857142854999999</v>
       </c>
-    </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T107">
+        <v>0.35916714862348098</v>
+      </c>
+    </row>
+    <row r="108" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>107</v>
       </c>
@@ -9995,8 +10323,11 @@
       <c r="S108">
         <v>60</v>
       </c>
-    </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T108">
+        <v>0.47368421052631499</v>
+      </c>
+    </row>
+    <row r="109" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>108</v>
       </c>
@@ -10051,8 +10382,11 @@
       <c r="S109">
         <v>72</v>
       </c>
-    </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T109">
+        <v>0.57085020242914897</v>
+      </c>
+    </row>
+    <row r="110" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>109</v>
       </c>
@@ -10110,8 +10444,11 @@
       <c r="S110">
         <v>14</v>
       </c>
-    </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T110">
+        <v>0.10121457489878501</v>
+      </c>
+    </row>
+    <row r="111" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>110</v>
       </c>
@@ -10166,8 +10503,11 @@
       <c r="S111">
         <v>3</v>
       </c>
-    </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T111">
+        <v>1.2145748987854201E-2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>111</v>
       </c>
@@ -10225,8 +10565,11 @@
       <c r="S112">
         <v>9</v>
       </c>
-    </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T112">
+        <v>6.0728744939271197E-2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>112</v>
       </c>
@@ -10281,8 +10624,11 @@
       <c r="S113">
         <v>13.676470587500001</v>
       </c>
-    </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T113">
+        <v>9.8594903542510104E-2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>113</v>
       </c>
@@ -10337,8 +10683,11 @@
       <c r="S114">
         <v>10</v>
       </c>
-    </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T114">
+        <v>6.8825910931174003E-2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>114</v>
       </c>
@@ -10393,8 +10742,11 @@
       <c r="S115">
         <v>16</v>
       </c>
-    </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T115">
+        <v>0.11740890688259099</v>
+      </c>
+    </row>
+    <row r="116" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>115</v>
       </c>
@@ -10449,8 +10801,11 @@
       <c r="S116">
         <v>6</v>
       </c>
-    </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T116">
+        <v>3.6437246963562701E-2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>116</v>
       </c>
@@ -10505,8 +10860,11 @@
       <c r="S117">
         <v>48</v>
       </c>
-    </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T117">
+        <v>0.376518218623481</v>
+      </c>
+    </row>
+    <row r="118" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>117</v>
       </c>
@@ -10561,8 +10919,11 @@
       <c r="S118">
         <v>6.6</v>
       </c>
-    </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T118">
+        <v>4.1295546558704398E-2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>118</v>
       </c>
@@ -10617,8 +10978,11 @@
       <c r="S119">
         <v>48</v>
       </c>
-    </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T119">
+        <v>0.376518218623481</v>
+      </c>
+    </row>
+    <row r="120" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>119</v>
       </c>
@@ -10676,8 +11040,11 @@
       <c r="S120">
         <v>75</v>
       </c>
-    </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T120">
+        <v>0.59514170040485803</v>
+      </c>
+    </row>
+    <row r="121" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>120</v>
       </c>
@@ -10732,8 +11099,11 @@
       <c r="S121">
         <v>9</v>
       </c>
-    </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T121">
+        <v>6.0728744939271197E-2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>121</v>
       </c>
@@ -10788,8 +11158,11 @@
       <c r="S122">
         <v>40.5</v>
       </c>
-    </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T122">
+        <v>0.31578947368421001</v>
+      </c>
+    </row>
+    <row r="123" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>122</v>
       </c>
@@ -10844,8 +11217,11 @@
       <c r="S123">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>123</v>
       </c>
@@ -10900,8 +11276,11 @@
       <c r="S124">
         <v>7.6999999995000001</v>
       </c>
-    </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T124">
+        <v>5.0202429145748899E-2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>124</v>
       </c>
@@ -10956,8 +11335,11 @@
       <c r="S125">
         <v>4</v>
       </c>
-    </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T125">
+        <v>2.0242914979756998E-2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>125</v>
       </c>
@@ -11012,8 +11394,11 @@
       <c r="S126">
         <v>1.7272727274999999</v>
       </c>
-    </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T126">
+        <v>1.84026499999999E-3</v>
+      </c>
+    </row>
+    <row r="127" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>126</v>
       </c>
@@ -11068,8 +11453,11 @@
       <c r="S127">
         <v>11.041666667499999</v>
       </c>
-    </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T127">
+        <v>7.7260458846153804E-2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>127</v>
       </c>
@@ -11124,8 +11512,11 @@
       <c r="S128">
         <v>31.5</v>
       </c>
-    </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T128">
+        <v>0.24291497975708501</v>
+      </c>
+    </row>
+    <row r="129" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>128</v>
       </c>
@@ -11180,8 +11571,11 @@
       <c r="S129">
         <v>5</v>
       </c>
-    </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T129">
+        <v>2.8340080971659899E-2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>129</v>
       </c>
@@ -11236,8 +11630,11 @@
       <c r="S130">
         <v>4.6875</v>
       </c>
-    </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T130">
+        <v>2.5809716599190201E-2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>130</v>
       </c>
@@ -11295,8 +11692,11 @@
       <c r="S131">
         <v>27</v>
       </c>
-    </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T131">
+        <v>0.206477732793522</v>
+      </c>
+    </row>
+    <row r="132" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>131</v>
       </c>
@@ -11351,8 +11751,11 @@
       <c r="S132">
         <v>3</v>
       </c>
-    </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T132">
+        <v>1.2145748987854201E-2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>132</v>
       </c>
@@ -11407,8 +11810,11 @@
       <c r="S133">
         <v>35</v>
       </c>
-    </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T133">
+        <v>0.271255060728744</v>
+      </c>
+    </row>
+    <row r="134" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>133</v>
       </c>
@@ -11463,8 +11869,11 @@
       <c r="S134">
         <v>10.5</v>
       </c>
-    </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T134">
+        <v>7.28744939271255E-2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>134</v>
       </c>
@@ -11519,8 +11928,11 @@
       <c r="S135">
         <v>2.0625</v>
       </c>
-    </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T135">
+        <v>4.5546558704453403E-3</v>
+      </c>
+    </row>
+    <row r="136" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>135</v>
       </c>
@@ -11575,8 +11987,11 @@
       <c r="S136">
         <v>4</v>
       </c>
-    </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T136">
+        <v>2.0242914979756998E-2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>136</v>
       </c>
@@ -11631,8 +12046,11 @@
       <c r="S137">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>137</v>
       </c>
@@ -11690,8 +12108,11 @@
       <c r="S138">
         <v>106.696428575</v>
       </c>
-    </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T138">
+        <v>0.85179294392712501</v>
+      </c>
+    </row>
+    <row r="139" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>138</v>
       </c>
@@ -11746,8 +12167,11 @@
       <c r="S139">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T139">
+        <v>2.4291497975708499E-2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>139</v>
       </c>
@@ -11802,8 +12226,11 @@
       <c r="S140">
         <v>8.6764705875000008</v>
       </c>
-    </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T140">
+        <v>5.8109073582995899E-2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>140</v>
       </c>
@@ -11861,8 +12288,11 @@
       <c r="S141">
         <v>30</v>
       </c>
-    </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T141">
+        <v>0.23076923076923</v>
+      </c>
+    </row>
+    <row r="142" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>141</v>
       </c>
@@ -11917,8 +12347,11 @@
       <c r="S142">
         <v>30</v>
       </c>
-    </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T142">
+        <v>0.23076923076923</v>
+      </c>
+    </row>
+    <row r="143" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>142</v>
       </c>
@@ -11973,8 +12406,11 @@
       <c r="S143">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T143">
+        <v>4.8582995951416998E-2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>143</v>
       </c>
@@ -12032,8 +12468,11 @@
       <c r="S144">
         <v>30</v>
       </c>
-    </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T144">
+        <v>0.23076923076923</v>
+      </c>
+    </row>
+    <row r="145" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>144</v>
       </c>
@@ -12088,8 +12527,11 @@
       <c r="S145">
         <v>26.4</v>
       </c>
-    </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T145">
+        <v>0.20161943319837999</v>
+      </c>
+    </row>
+    <row r="146" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>145</v>
       </c>
@@ -12147,8 +12589,11 @@
       <c r="S146">
         <v>50</v>
       </c>
-    </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T146">
+        <v>0.39271255060728699</v>
+      </c>
+    </row>
+    <row r="147" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>146</v>
       </c>
@@ -12203,8 +12648,11 @@
       <c r="S147">
         <v>12</v>
       </c>
-    </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T147">
+        <v>8.5020242914979699E-2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>147</v>
       </c>
@@ -12262,8 +12710,11 @@
       <c r="S148">
         <v>65.357142859999996</v>
       </c>
-    </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T148">
+        <v>0.51706188550607202</v>
+      </c>
+    </row>
+    <row r="149" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>148</v>
       </c>
@@ -12321,8 +12772,11 @@
       <c r="S149">
         <v>35.571428570000002</v>
       </c>
-    </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T149">
+        <v>0.27588201271254997</v>
+      </c>
+    </row>
+    <row r="150" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>149</v>
       </c>
@@ -12380,8 +12834,11 @@
       <c r="S150">
         <v>94.196428574999999</v>
       </c>
-    </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T150">
+        <v>0.75057836902833996</v>
+      </c>
+    </row>
+    <row r="151" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>150</v>
       </c>
@@ -12439,8 +12896,11 @@
       <c r="S151">
         <v>15</v>
       </c>
-    </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T151">
+        <v>0.109311740890688</v>
+      </c>
+    </row>
+    <row r="152" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>151</v>
       </c>
@@ -12495,8 +12955,11 @@
       <c r="S152">
         <v>3</v>
       </c>
-    </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T152">
+        <v>1.2145748987854201E-2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>152</v>
       </c>
@@ -12554,8 +13017,11 @@
       <c r="S153">
         <v>94.196428574999999</v>
       </c>
-    </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T153">
+        <v>0.75057836902833996</v>
+      </c>
+    </row>
+    <row r="154" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>153</v>
       </c>
@@ -12610,8 +13076,11 @@
       <c r="S154">
         <v>9</v>
       </c>
-    </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T154">
+        <v>6.0728744939271197E-2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>154</v>
       </c>
@@ -12666,8 +13135,11 @@
       <c r="S155">
         <v>8.4</v>
       </c>
-    </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T155">
+        <v>5.58704453441295E-2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>155</v>
       </c>
@@ -12725,8 +13197,11 @@
       <c r="S156">
         <v>70</v>
       </c>
-    </row>
-    <row r="157" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T156">
+        <v>0.55465587044534403</v>
+      </c>
+    </row>
+    <row r="157" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>156</v>
       </c>
@@ -12781,8 +13256,11 @@
       <c r="S157">
         <v>16</v>
       </c>
-    </row>
-    <row r="158" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T157">
+        <v>0.11740890688259099</v>
+      </c>
+    </row>
+    <row r="158" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>157</v>
       </c>
@@ -12837,8 +13315,11 @@
       <c r="S158">
         <v>4</v>
       </c>
-    </row>
-    <row r="159" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T158">
+        <v>2.0242914979756998E-2</v>
+      </c>
+    </row>
+    <row r="159" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>158</v>
       </c>
@@ -12896,8 +13377,11 @@
       <c r="S159">
         <v>88.928571425000001</v>
       </c>
-    </row>
-    <row r="160" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T159">
+        <v>0.70792365526315704</v>
+      </c>
+    </row>
+    <row r="160" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>159</v>
       </c>
@@ -12955,8 +13439,11 @@
       <c r="S160">
         <v>94.196428574999999</v>
       </c>
-    </row>
-    <row r="161" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T160">
+        <v>0.75057836902833996</v>
+      </c>
+    </row>
+    <row r="161" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>160</v>
       </c>
@@ -13011,8 +13498,11 @@
       <c r="S161">
         <v>5</v>
       </c>
-    </row>
-    <row r="162" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T161">
+        <v>2.8340080971659899E-2</v>
+      </c>
+    </row>
+    <row r="162" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>161</v>
       </c>
@@ -13067,8 +13557,11 @@
       <c r="S162">
         <v>2</v>
       </c>
-    </row>
-    <row r="163" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T162">
+        <v>4.0485829959514101E-3</v>
+      </c>
+    </row>
+    <row r="163" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>162</v>
       </c>
@@ -13123,8 +13616,11 @@
       <c r="S163">
         <v>12.9</v>
       </c>
-    </row>
-    <row r="164" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T163">
+        <v>9.2307692307692299E-2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>163</v>
       </c>
@@ -13179,8 +13675,11 @@
       <c r="S164">
         <v>2</v>
       </c>
-    </row>
-    <row r="165" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T164">
+        <v>4.0485829959514101E-3</v>
+      </c>
+    </row>
+    <row r="165" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>164</v>
       </c>
@@ -13235,8 +13734,11 @@
       <c r="S165">
         <v>6.1764705874999999</v>
       </c>
-    </row>
-    <row r="166" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T165">
+        <v>3.7866158603238803E-2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>165</v>
       </c>
@@ -13294,8 +13796,11 @@
       <c r="S166">
         <v>62.5</v>
       </c>
-    </row>
-    <row r="167" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T166">
+        <v>0.49392712550607198</v>
+      </c>
+    </row>
+    <row r="167" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>166</v>
       </c>
@@ -13350,8 +13855,11 @@
       <c r="S167">
         <v>6.9411764700000003</v>
       </c>
-    </row>
-    <row r="168" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T167">
+        <v>4.4058109068825901E-2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>167</v>
       </c>
@@ -13406,8 +13914,11 @@
       <c r="S168">
         <v>14</v>
       </c>
-    </row>
-    <row r="169" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T168">
+        <v>0.10121457489878501</v>
+      </c>
+    </row>
+    <row r="169" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>168</v>
       </c>
@@ -13462,8 +13973,11 @@
       <c r="S169">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="170" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T169">
+        <v>8.0971659919028306E-3</v>
+      </c>
+    </row>
+    <row r="170" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>169</v>
       </c>
@@ -13518,8 +14032,11 @@
       <c r="S170">
         <v>10.5</v>
       </c>
-    </row>
-    <row r="171" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T170">
+        <v>7.28744939271255E-2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>170</v>
       </c>
@@ -13574,8 +14091,11 @@
       <c r="S171">
         <v>8</v>
       </c>
-    </row>
-    <row r="172" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T171">
+        <v>5.2631578947368397E-2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>171</v>
       </c>
@@ -13630,8 +14150,11 @@
       <c r="S172">
         <v>3</v>
       </c>
-    </row>
-    <row r="173" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T172">
+        <v>1.2145748987854201E-2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>172</v>
       </c>
@@ -13686,8 +14209,11 @@
       <c r="S173">
         <v>5</v>
       </c>
-    </row>
-    <row r="174" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T173">
+        <v>2.8340080971659899E-2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>173</v>
       </c>
@@ -13745,8 +14271,11 @@
       <c r="S174">
         <v>40</v>
       </c>
-    </row>
-    <row r="175" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T174">
+        <v>0.311740890688259</v>
+      </c>
+    </row>
+    <row r="175" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>174</v>
       </c>
@@ -13801,8 +14330,11 @@
       <c r="S175">
         <v>45</v>
       </c>
-    </row>
-    <row r="176" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T175">
+        <v>0.352226720647773</v>
+      </c>
+    </row>
+    <row r="176" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>175</v>
       </c>
@@ -13857,8 +14389,11 @@
       <c r="S176">
         <v>13</v>
       </c>
-    </row>
-    <row r="177" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T176">
+        <v>9.3117408906882596E-2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>176</v>
       </c>
@@ -13913,8 +14448,11 @@
       <c r="S177">
         <v>6</v>
       </c>
-    </row>
-    <row r="178" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T177">
+        <v>3.6437246963562701E-2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>177</v>
       </c>
@@ -13969,8 +14507,11 @@
       <c r="S178">
         <v>15.75</v>
       </c>
-    </row>
-    <row r="179" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T178">
+        <v>0.115384615384615</v>
+      </c>
+    </row>
+    <row r="179" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>178</v>
       </c>
@@ -14025,8 +14566,11 @@
       <c r="S179">
         <v>7</v>
       </c>
-    </row>
-    <row r="180" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T179">
+        <v>4.4534412955465501E-2</v>
+      </c>
+    </row>
+    <row r="180" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>179</v>
       </c>
@@ -14081,8 +14625,11 @@
       <c r="S180">
         <v>15</v>
       </c>
-    </row>
-    <row r="181" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T180">
+        <v>0.109311740890688</v>
+      </c>
+    </row>
+    <row r="181" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>180</v>
       </c>
@@ -14137,8 +14684,11 @@
       <c r="S181">
         <v>6</v>
       </c>
-    </row>
-    <row r="182" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T181">
+        <v>3.6437246963562701E-2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>181</v>
       </c>
@@ -14193,8 +14743,11 @@
       <c r="S182">
         <v>4.4705882350000001</v>
       </c>
-    </row>
-    <row r="183" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T182">
+        <v>2.4053346032388599E-2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>182</v>
       </c>
@@ -14249,8 +14802,11 @@
       <c r="S183">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="184" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T183">
+        <v>4.8582995951416998E-2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>183</v>
       </c>
@@ -14305,8 +14861,11 @@
       <c r="S184">
         <v>7</v>
       </c>
-    </row>
-    <row r="185" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T184">
+        <v>4.4534412955465501E-2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>184</v>
       </c>
@@ -14361,8 +14920,11 @@
       <c r="S185">
         <v>5.2058823524999998</v>
       </c>
-    </row>
-    <row r="186" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T185">
+        <v>3.00071445546558E-2</v>
+      </c>
+    </row>
+    <row r="186" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>185</v>
       </c>
@@ -14420,8 +14982,11 @@
       <c r="S186">
         <v>100</v>
       </c>
-    </row>
-    <row r="187" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T186">
+        <v>0.79757085020242902</v>
+      </c>
+    </row>
+    <row r="187" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>186</v>
       </c>
@@ -14476,8 +15041,11 @@
       <c r="S187">
         <v>5</v>
       </c>
-    </row>
-    <row r="188" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T187">
+        <v>2.8340080971659899E-2</v>
+      </c>
+    </row>
+    <row r="188" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>187</v>
       </c>
@@ -14532,8 +15100,11 @@
       <c r="S188">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="189" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T188">
+        <v>4.8582995951416998E-2</v>
+      </c>
+    </row>
+    <row r="189" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>188</v>
       </c>
@@ -14588,8 +15159,11 @@
       <c r="S189">
         <v>60</v>
       </c>
-    </row>
-    <row r="190" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T189">
+        <v>0.47368421052631499</v>
+      </c>
+    </row>
+    <row r="190" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>189</v>
       </c>
@@ -14644,8 +15218,11 @@
       <c r="S190">
         <v>1.7272727274999999</v>
       </c>
-    </row>
-    <row r="191" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T190">
+        <v>1.84026499999999E-3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>190</v>
       </c>
@@ -14700,8 +15277,11 @@
       <c r="S191">
         <v>16</v>
       </c>
-    </row>
-    <row r="192" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T191">
+        <v>0.11740890688259099</v>
+      </c>
+    </row>
+    <row r="192" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>191</v>
       </c>
@@ -14756,8 +15336,11 @@
       <c r="S192">
         <v>6.1875</v>
       </c>
-    </row>
-    <row r="193" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T192">
+        <v>3.7955465587044497E-2</v>
+      </c>
+    </row>
+    <row r="193" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>192</v>
       </c>
@@ -14812,8 +15395,11 @@
       <c r="S193">
         <v>4.4705882350000001</v>
       </c>
-    </row>
-    <row r="194" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T193">
+        <v>2.4053346032388599E-2</v>
+      </c>
+    </row>
+    <row r="194" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>193</v>
       </c>
@@ -14871,8 +15457,11 @@
       <c r="S194">
         <v>90.277777775000004</v>
       </c>
-    </row>
-    <row r="195" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T194">
+        <v>0.71884840303643704</v>
+      </c>
+    </row>
+    <row r="195" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>194</v>
       </c>
@@ -14927,8 +15516,11 @@
       <c r="S195">
         <v>11.176470587500001</v>
       </c>
-    </row>
-    <row r="196" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T195">
+        <v>7.8351988562752994E-2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>195</v>
       </c>
@@ -14983,8 +15575,11 @@
       <c r="S196">
         <v>11.176470587500001</v>
       </c>
-    </row>
-    <row r="197" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T196">
+        <v>7.8351988562752994E-2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>196</v>
       </c>
@@ -15039,8 +15634,11 @@
       <c r="S197">
         <v>3</v>
       </c>
-    </row>
-    <row r="198" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T197">
+        <v>1.2145748987854201E-2</v>
+      </c>
+    </row>
+    <row r="198" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>197</v>
       </c>
@@ -15095,8 +15693,11 @@
       <c r="S198">
         <v>14</v>
       </c>
-    </row>
-    <row r="199" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T198">
+        <v>0.10121457489878501</v>
+      </c>
+    </row>
+    <row r="199" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>198</v>
       </c>
@@ -15154,8 +15755,11 @@
       <c r="S199">
         <v>106.696428575</v>
       </c>
-    </row>
-    <row r="200" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T199">
+        <v>0.85179294392712501</v>
+      </c>
+    </row>
+    <row r="200" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>199</v>
       </c>
@@ -15213,8 +15817,11 @@
       <c r="S200">
         <v>17.5</v>
       </c>
-    </row>
-    <row r="201" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T200">
+        <v>0.12955465587044501</v>
+      </c>
+    </row>
+    <row r="201" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>200</v>
       </c>
@@ -15269,8 +15876,11 @@
       <c r="S201">
         <v>3</v>
       </c>
-    </row>
-    <row r="202" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T201">
+        <v>1.2145748987854201E-2</v>
+      </c>
+    </row>
+    <row r="202" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A202">
         <v>201</v>
       </c>
@@ -15325,8 +15935,11 @@
       <c r="S202">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="203" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T202">
+        <v>1.6194331983805599E-2</v>
+      </c>
+    </row>
+    <row r="203" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A203">
         <v>202</v>
       </c>
@@ -15381,8 +15994,11 @@
       <c r="S203">
         <v>7</v>
       </c>
-    </row>
-    <row r="204" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T203">
+        <v>4.4534412955465501E-2</v>
+      </c>
+    </row>
+    <row r="204" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>203</v>
       </c>
@@ -15440,8 +16056,11 @@
       <c r="S204">
         <v>125</v>
       </c>
-    </row>
-    <row r="205" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T204">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A205">
         <v>204</v>
       </c>
@@ -15499,8 +16118,11 @@
       <c r="S205">
         <v>112.5</v>
       </c>
-    </row>
-    <row r="206" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T205">
+        <v>0.89878542510121395</v>
+      </c>
+    </row>
+    <row r="206" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>205</v>
       </c>
@@ -15555,8 +16177,11 @@
       <c r="S206">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="207" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T206">
+        <v>1.6194331983805599E-2</v>
+      </c>
+    </row>
+    <row r="207" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>206</v>
       </c>
@@ -15611,8 +16236,11 @@
       <c r="S207">
         <v>8.6363636375000006</v>
       </c>
-    </row>
-    <row r="208" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T207">
+        <v>5.7784320951417001E-2</v>
+      </c>
+    </row>
+    <row r="208" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A208">
         <v>207</v>
       </c>
@@ -15667,8 +16295,11 @@
       <c r="S208">
         <v>90</v>
       </c>
-    </row>
-    <row r="209" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T208">
+        <v>0.71659919028340002</v>
+      </c>
+    </row>
+    <row r="209" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A209">
         <v>208</v>
       </c>
@@ -15723,8 +16354,11 @@
       <c r="S209">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="210" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T209">
+        <v>8.0971659919028306E-3</v>
+      </c>
+    </row>
+    <row r="210" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A210">
         <v>209</v>
       </c>
@@ -15779,8 +16413,11 @@
       <c r="S210">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="211" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T210">
+        <v>8.0971659919028306E-3</v>
+      </c>
+    </row>
+    <row r="211" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>210</v>
       </c>
@@ -15835,8 +16472,11 @@
       <c r="S211">
         <v>100</v>
       </c>
-    </row>
-    <row r="212" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T211">
+        <v>0.79757085020242902</v>
+      </c>
+    </row>
+    <row r="212" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A212">
         <v>211</v>
       </c>
@@ -15891,8 +16531,11 @@
       <c r="S212">
         <v>12</v>
       </c>
-    </row>
-    <row r="213" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T212">
+        <v>8.5020242914979699E-2</v>
+      </c>
+    </row>
+    <row r="213" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A213">
         <v>212</v>
       </c>
@@ -15950,8 +16593,11 @@
       <c r="S213">
         <v>52.5</v>
       </c>
-    </row>
-    <row r="214" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T213">
+        <v>0.41295546558704399</v>
+      </c>
+    </row>
+    <row r="214" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A214">
         <v>213</v>
       </c>
@@ -16006,8 +16652,11 @@
       <c r="S214">
         <v>35</v>
       </c>
-    </row>
-    <row r="215" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T214">
+        <v>0.271255060728744</v>
+      </c>
+    </row>
+    <row r="215" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A215">
         <v>214</v>
       </c>
@@ -16062,8 +16711,11 @@
       <c r="S215">
         <v>3</v>
       </c>
-    </row>
-    <row r="216" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T215">
+        <v>1.2145748987854201E-2</v>
+      </c>
+    </row>
+    <row r="216" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>215</v>
       </c>
@@ -16118,8 +16770,11 @@
       <c r="S216">
         <v>9</v>
       </c>
-    </row>
-    <row r="217" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T216">
+        <v>6.0728744939271197E-2</v>
+      </c>
+    </row>
+    <row r="217" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A217">
         <v>216</v>
       </c>
@@ -16174,8 +16829,11 @@
       <c r="S217">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="218" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T217">
+        <v>8.0971659919028306E-3</v>
+      </c>
+    </row>
+    <row r="218" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A218">
         <v>217</v>
       </c>
@@ -16230,8 +16888,11 @@
       <c r="S218">
         <v>4</v>
       </c>
-    </row>
-    <row r="219" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T218">
+        <v>2.0242914979756998E-2</v>
+      </c>
+    </row>
+    <row r="219" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A219">
         <v>218</v>
       </c>
@@ -16286,8 +16947,11 @@
       <c r="S219">
         <v>27</v>
       </c>
-    </row>
-    <row r="220" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T219">
+        <v>0.206477732793522</v>
+      </c>
+    </row>
+    <row r="220" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A220">
         <v>219</v>
       </c>
@@ -16342,8 +17006,11 @@
       <c r="S220">
         <v>33</v>
       </c>
-    </row>
-    <row r="221" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T220">
+        <v>0.25506072874493901</v>
+      </c>
+    </row>
+    <row r="221" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A221">
         <v>220</v>
       </c>
@@ -16398,8 +17065,11 @@
       <c r="S221">
         <v>2</v>
       </c>
-    </row>
-    <row r="222" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T221">
+        <v>4.0485829959514101E-3</v>
+      </c>
+    </row>
+    <row r="222" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A222">
         <v>221</v>
       </c>
@@ -16454,8 +17124,11 @@
       <c r="S222">
         <v>3</v>
       </c>
-    </row>
-    <row r="223" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T222">
+        <v>1.2145748987854201E-2</v>
+      </c>
+    </row>
+    <row r="223" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A223">
         <v>222</v>
       </c>
@@ -16513,8 +17186,11 @@
       <c r="S223">
         <v>27</v>
       </c>
-    </row>
-    <row r="224" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T223">
+        <v>0.206477732793522</v>
+      </c>
+    </row>
+    <row r="224" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A224">
         <v>223</v>
       </c>
@@ -16572,8 +17248,11 @@
       <c r="S224">
         <v>75</v>
       </c>
-    </row>
-    <row r="225" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T224">
+        <v>0.59514170040485803</v>
+      </c>
+    </row>
+    <row r="225" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>224</v>
       </c>
@@ -16628,8 +17307,11 @@
       <c r="S225">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="226" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T225">
+        <v>1.6194331983805599E-2</v>
+      </c>
+    </row>
+    <row r="226" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A226">
         <v>225</v>
       </c>
@@ -16684,8 +17366,11 @@
       <c r="S226">
         <v>10</v>
       </c>
-    </row>
-    <row r="227" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T226">
+        <v>6.8825910931174003E-2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>226</v>
       </c>
@@ -16743,8 +17428,11 @@
       <c r="S227">
         <v>20</v>
       </c>
-    </row>
-    <row r="228" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T227">
+        <v>0.14979757085020201</v>
+      </c>
+    </row>
+    <row r="228" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>227</v>
       </c>
@@ -16799,8 +17487,11 @@
       <c r="S228">
         <v>48</v>
       </c>
-    </row>
-    <row r="229" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T228">
+        <v>0.376518218623481</v>
+      </c>
+    </row>
+    <row r="229" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>228</v>
       </c>
@@ -16858,8 +17549,11 @@
       <c r="S229">
         <v>62.5</v>
       </c>
-    </row>
-    <row r="230" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T229">
+        <v>0.49392712550607198</v>
+      </c>
+    </row>
+    <row r="230" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>229</v>
       </c>
@@ -16914,8 +17608,11 @@
       <c r="S230">
         <v>64</v>
       </c>
-    </row>
-    <row r="231" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T230">
+        <v>0.50607287449392702</v>
+      </c>
+    </row>
+    <row r="231" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A231">
         <v>230</v>
       </c>
@@ -16970,8 +17667,11 @@
       <c r="S231">
         <v>8.8333333340000006</v>
       </c>
-    </row>
-    <row r="232" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T231">
+        <v>5.9379217279352199E-2</v>
+      </c>
+    </row>
+    <row r="232" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A232">
         <v>231</v>
       </c>
@@ -17026,8 +17726,11 @@
       <c r="S232">
         <v>12</v>
       </c>
-    </row>
-    <row r="233" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T232">
+        <v>8.5020242914979699E-2</v>
+      </c>
+    </row>
+    <row r="233" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A233">
         <v>232</v>
       </c>
@@ -17082,8 +17785,11 @@
       <c r="S233">
         <v>9</v>
       </c>
-    </row>
-    <row r="234" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T233">
+        <v>6.0728744939271197E-2</v>
+      </c>
+    </row>
+    <row r="234" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A234">
         <v>233</v>
       </c>
@@ -17141,8 +17847,11 @@
       <c r="S234">
         <v>94.196428574999999</v>
       </c>
-    </row>
-    <row r="235" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T234">
+        <v>0.75057836902833996</v>
+      </c>
+    </row>
+    <row r="235" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A235">
         <v>234</v>
       </c>
@@ -17200,8 +17909,11 @@
       <c r="S235">
         <v>62.5</v>
       </c>
-    </row>
-    <row r="236" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T235">
+        <v>0.49392712550607198</v>
+      </c>
+    </row>
+    <row r="236" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A236">
         <v>235</v>
       </c>
@@ -17256,8 +17968,11 @@
       <c r="S236">
         <v>14</v>
       </c>
-    </row>
-    <row r="237" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T236">
+        <v>0.10121457489878501</v>
+      </c>
+    </row>
+    <row r="237" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A237">
         <v>236</v>
       </c>
@@ -17312,8 +18027,11 @@
       <c r="S237">
         <v>3</v>
       </c>
-    </row>
-    <row r="238" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T237">
+        <v>1.2145748987854201E-2</v>
+      </c>
+    </row>
+    <row r="238" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A238">
         <v>237</v>
       </c>
@@ -17368,8 +18086,11 @@
       <c r="S238">
         <v>12</v>
       </c>
-    </row>
-    <row r="239" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T238">
+        <v>8.5020242914979699E-2</v>
+      </c>
+    </row>
+    <row r="239" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A239">
         <v>238</v>
       </c>
@@ -17427,8 +18148,11 @@
       <c r="S239">
         <v>36</v>
       </c>
-    </row>
-    <row r="240" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T239">
+        <v>0.27935222672064702</v>
+      </c>
+    </row>
+    <row r="240" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A240">
         <v>239</v>
       </c>
@@ -17483,8 +18207,11 @@
       <c r="S240">
         <v>27</v>
       </c>
-    </row>
-    <row r="241" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T240">
+        <v>0.206477732793522</v>
+      </c>
+    </row>
+    <row r="241" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A241">
         <v>240</v>
       </c>
@@ -17539,8 +18266,11 @@
       <c r="S241">
         <v>17.5</v>
       </c>
-    </row>
-    <row r="242" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T241">
+        <v>0.12955465587044501</v>
+      </c>
+    </row>
+    <row r="242" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A242">
         <v>241</v>
       </c>
@@ -17598,8 +18328,11 @@
       <c r="S242">
         <v>37.5</v>
       </c>
-    </row>
-    <row r="243" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T242">
+        <v>0.291497975708502</v>
+      </c>
+    </row>
+    <row r="243" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A243">
         <v>242</v>
       </c>
@@ -17654,8 +18387,11 @@
       <c r="S243">
         <v>8</v>
       </c>
-    </row>
-    <row r="244" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T243">
+        <v>5.2631578947368397E-2</v>
+      </c>
+    </row>
+    <row r="244" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A244">
         <v>243</v>
       </c>
@@ -17710,8 +18446,11 @@
       <c r="S244">
         <v>125</v>
       </c>
-    </row>
-    <row r="245" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T244">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A245">
         <v>244</v>
       </c>
@@ -17769,8 +18508,11 @@
       <c r="S245">
         <v>50</v>
       </c>
-    </row>
-    <row r="246" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T245">
+        <v>0.39271255060728699</v>
+      </c>
+    </row>
+    <row r="246" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A246">
         <v>245</v>
       </c>
@@ -17825,8 +18567,11 @@
       <c r="S246">
         <v>9.9444444440000002</v>
       </c>
-    </row>
-    <row r="247" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T246">
+        <v>6.8376068372469595E-2</v>
+      </c>
+    </row>
+    <row r="247" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A247">
         <v>246</v>
       </c>
@@ -17884,8 +18629,11 @@
       <c r="S247">
         <v>94.196428574999999</v>
       </c>
-    </row>
-    <row r="248" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T247">
+        <v>0.75057836902833996</v>
+      </c>
+    </row>
+    <row r="248" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A248">
         <v>247</v>
       </c>
@@ -17940,8 +18688,11 @@
       <c r="S248">
         <v>6</v>
       </c>
-    </row>
-    <row r="249" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T248">
+        <v>3.6437246963562701E-2</v>
+      </c>
+    </row>
+    <row r="249" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A249">
         <v>248</v>
       </c>
@@ -17996,8 +18747,11 @@
       <c r="S249">
         <v>75</v>
       </c>
-    </row>
-    <row r="250" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T249">
+        <v>0.59514170040485803</v>
+      </c>
+    </row>
+    <row r="250" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A250">
         <v>249</v>
       </c>
@@ -18052,8 +18806,11 @@
       <c r="S250">
         <v>6</v>
       </c>
-    </row>
-    <row r="251" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T250">
+        <v>3.6437246963562701E-2</v>
+      </c>
+    </row>
+    <row r="251" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A251">
         <v>250</v>
       </c>
@@ -18108,8 +18865,11 @@
       <c r="S251">
         <v>7</v>
       </c>
-    </row>
-    <row r="252" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T251">
+        <v>4.4534412955465501E-2</v>
+      </c>
+    </row>
+    <row r="252" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A252">
         <v>251</v>
       </c>
@@ -18164,8 +18924,11 @@
       <c r="S252">
         <v>13.676470587500001</v>
       </c>
-    </row>
-    <row r="253" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T252">
+        <v>9.8594903542510104E-2</v>
+      </c>
+    </row>
+    <row r="253" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A253">
         <v>252</v>
       </c>
@@ -18220,8 +18983,11 @@
       <c r="S253">
         <v>6.9411764700000003</v>
       </c>
-    </row>
-    <row r="254" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T253">
+        <v>4.4058109068825901E-2</v>
+      </c>
+    </row>
+    <row r="254" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A254">
         <v>253</v>
       </c>
@@ -18276,8 +19042,11 @@
       <c r="S254">
         <v>18</v>
       </c>
-    </row>
-    <row r="255" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T254">
+        <v>0.133603238866396</v>
+      </c>
+    </row>
+    <row r="255" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A255">
         <v>254</v>
       </c>
@@ -18332,8 +19101,11 @@
       <c r="S255">
         <v>50</v>
       </c>
-    </row>
-    <row r="256" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T255">
+        <v>0.39271255060728699</v>
+      </c>
+    </row>
+    <row r="256" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A256">
         <v>255</v>
       </c>
@@ -18388,8 +19160,11 @@
       <c r="S256">
         <v>15</v>
       </c>
-    </row>
-    <row r="257" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T256">
+        <v>0.109311740890688</v>
+      </c>
+    </row>
+    <row r="257" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A257">
         <v>256</v>
       </c>
@@ -18444,8 +19219,11 @@
       <c r="S257">
         <v>3</v>
       </c>
-    </row>
-    <row r="258" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T257">
+        <v>1.2145748987854201E-2</v>
+      </c>
+    </row>
+    <row r="258" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A258">
         <v>257</v>
       </c>
@@ -18500,8 +19278,11 @@
       <c r="S258">
         <v>67.5</v>
       </c>
-    </row>
-    <row r="259" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T258">
+        <v>0.53441295546558698</v>
+      </c>
+    </row>
+    <row r="259" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A259">
         <v>258</v>
       </c>
@@ -18556,8 +19337,11 @@
       <c r="S259">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="260" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T259">
+        <v>8.0971659919028306E-3</v>
+      </c>
+    </row>
+    <row r="260" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A260">
         <v>259</v>
       </c>
@@ -18612,8 +19396,11 @@
       <c r="S260">
         <v>75.357142859999996</v>
       </c>
-    </row>
-    <row r="261" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T260">
+        <v>0.59803354542510101</v>
+      </c>
+    </row>
+    <row r="261" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A261">
         <v>260</v>
       </c>
@@ -18668,8 +19455,11 @@
       <c r="S261">
         <v>14</v>
       </c>
-    </row>
-    <row r="262" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T261">
+        <v>0.10121457489878501</v>
+      </c>
+    </row>
+    <row r="262" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A262">
         <v>261</v>
       </c>
@@ -18724,8 +19514,11 @@
       <c r="S262">
         <v>16</v>
       </c>
-    </row>
-    <row r="263" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T262">
+        <v>0.11740890688259099</v>
+      </c>
+    </row>
+    <row r="263" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A263">
         <v>262</v>
       </c>
@@ -18780,8 +19573,11 @@
       <c r="S263">
         <v>27</v>
       </c>
-    </row>
-    <row r="264" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T263">
+        <v>0.206477732793522</v>
+      </c>
+    </row>
+    <row r="264" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A264">
         <v>263</v>
       </c>
@@ -18836,8 +19632,11 @@
       <c r="S264">
         <v>7</v>
       </c>
-    </row>
-    <row r="265" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T264">
+        <v>4.4534412955465501E-2</v>
+      </c>
+    </row>
+    <row r="265" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A265">
         <v>264</v>
       </c>
@@ -18895,8 +19694,11 @@
       <c r="S265">
         <v>94.196428574999999</v>
       </c>
-    </row>
-    <row r="266" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T265">
+        <v>0.75057836902833996</v>
+      </c>
+    </row>
+    <row r="266" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A266">
         <v>265</v>
       </c>
@@ -18951,8 +19753,11 @@
       <c r="S266">
         <v>3</v>
       </c>
-    </row>
-    <row r="267" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T266">
+        <v>1.2145748987854201E-2</v>
+      </c>
+    </row>
+    <row r="267" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A267">
         <v>266</v>
       </c>
@@ -19007,8 +19812,11 @@
       <c r="S267">
         <v>6.6250000005</v>
       </c>
-    </row>
-    <row r="268" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T267">
+        <v>4.1497975712550601E-2</v>
+      </c>
+    </row>
+    <row r="268" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A268">
         <v>267</v>
       </c>
@@ -19063,8 +19871,11 @@
       <c r="S268">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="269" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T268">
+        <v>1.6194331983805599E-2</v>
+      </c>
+    </row>
+    <row r="269" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A269">
         <v>268</v>
       </c>
@@ -19122,8 +19933,11 @@
       <c r="S269">
         <v>17.5</v>
       </c>
-    </row>
-    <row r="270" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T269">
+        <v>0.12955465587044501</v>
+      </c>
+    </row>
+    <row r="270" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A270">
         <v>269</v>
       </c>
@@ -19178,8 +19992,11 @@
       <c r="S270">
         <v>8</v>
       </c>
-    </row>
-    <row r="271" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T270">
+        <v>5.2631578947368397E-2</v>
+      </c>
+    </row>
+    <row r="271" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A271">
         <v>270</v>
       </c>
@@ -19234,8 +20051,11 @@
       <c r="S271">
         <v>1.5625</v>
       </c>
-    </row>
-    <row r="272" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T271" s="2">
+        <v>5.0607287449392702E-4</v>
+      </c>
+    </row>
+    <row r="272" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A272">
         <v>271</v>
       </c>
@@ -19290,8 +20110,11 @@
       <c r="S272">
         <v>14</v>
       </c>
-    </row>
-    <row r="273" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T272">
+        <v>0.10121457489878501</v>
+      </c>
+    </row>
+    <row r="273" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A273">
         <v>272</v>
       </c>
@@ -19346,8 +20169,11 @@
       <c r="S273">
         <v>9</v>
       </c>
-    </row>
-    <row r="274" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T273">
+        <v>6.0728744939271197E-2</v>
+      </c>
+    </row>
+    <row r="274" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A274">
         <v>273</v>
       </c>
@@ -19405,8 +20231,11 @@
       <c r="S274">
         <v>62.5</v>
       </c>
-    </row>
-    <row r="275" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T274">
+        <v>0.49392712550607198</v>
+      </c>
+    </row>
+    <row r="275" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A275">
         <v>274</v>
       </c>
@@ -19464,8 +20293,11 @@
       <c r="S275">
         <v>64.017857144999994</v>
       </c>
-    </row>
-    <row r="276" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T275">
+        <v>0.50621746676113299</v>
+      </c>
+    </row>
+    <row r="276" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A276">
         <v>275</v>
       </c>
@@ -19520,8 +20352,11 @@
       <c r="S276">
         <v>4</v>
       </c>
-    </row>
-    <row r="277" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T276">
+        <v>2.0242914979756998E-2</v>
+      </c>
+    </row>
+    <row r="277" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A277">
         <v>276</v>
       </c>
@@ -19576,8 +20411,11 @@
       <c r="S277">
         <v>10</v>
       </c>
-    </row>
-    <row r="278" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T277">
+        <v>6.8825910931174003E-2</v>
+      </c>
+    </row>
+    <row r="278" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A278">
         <v>277</v>
       </c>
@@ -19632,8 +20470,11 @@
       <c r="S278">
         <v>6</v>
       </c>
-    </row>
-    <row r="279" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T278">
+        <v>3.6437246963562701E-2</v>
+      </c>
+    </row>
+    <row r="279" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A279">
         <v>278</v>
       </c>
@@ -19688,8 +20529,11 @@
       <c r="S279">
         <v>6.1764705874999999</v>
       </c>
-    </row>
-    <row r="280" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T279">
+        <v>3.7866158603238803E-2</v>
+      </c>
+    </row>
+    <row r="280" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A280">
         <v>279</v>
       </c>
@@ -19747,8 +20591,11 @@
       <c r="S280">
         <v>50</v>
       </c>
-    </row>
-    <row r="281" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T280">
+        <v>0.39271255060728699</v>
+      </c>
+    </row>
+    <row r="281" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A281">
         <v>280</v>
       </c>
@@ -19803,8 +20650,11 @@
       <c r="S281">
         <v>12.5</v>
       </c>
-    </row>
-    <row r="282" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T281">
+        <v>8.9068825910931099E-2</v>
+      </c>
+    </row>
+    <row r="282" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A282">
         <v>281</v>
       </c>
@@ -19862,8 +20712,11 @@
       <c r="S282">
         <v>60</v>
       </c>
-    </row>
-    <row r="283" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T282">
+        <v>0.47368421052631499</v>
+      </c>
+    </row>
+    <row r="283" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A283">
         <v>282</v>
       </c>
@@ -19921,8 +20774,11 @@
       <c r="S283">
         <v>30</v>
       </c>
-    </row>
-    <row r="284" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T283">
+        <v>0.23076923076923</v>
+      </c>
+    </row>
+    <row r="284" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A284">
         <v>283</v>
       </c>
@@ -19980,8 +20836,11 @@
       <c r="S284">
         <v>88.928571425000001</v>
       </c>
-    </row>
-    <row r="285" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T284">
+        <v>0.70792365526315704</v>
+      </c>
+    </row>
+    <row r="285" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A285">
         <v>284</v>
       </c>
@@ -20036,8 +20895,11 @@
       <c r="S285">
         <v>8</v>
       </c>
-    </row>
-    <row r="286" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T285">
+        <v>5.2631578947368397E-2</v>
+      </c>
+    </row>
+    <row r="286" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A286">
         <v>285</v>
       </c>
@@ -20092,8 +20954,11 @@
       <c r="S286">
         <v>10</v>
       </c>
-    </row>
-    <row r="287" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T286">
+        <v>6.8825910931174003E-2</v>
+      </c>
+    </row>
+    <row r="287" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A287">
         <v>286</v>
       </c>
@@ -20148,8 +21013,11 @@
       <c r="S287">
         <v>9</v>
       </c>
-    </row>
-    <row r="288" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T287">
+        <v>6.0728744939271197E-2</v>
+      </c>
+    </row>
+    <row r="288" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A288">
         <v>287</v>
       </c>
@@ -20204,8 +21072,11 @@
       <c r="S288">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="289" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T288">
+        <v>1.6194331983805599E-2</v>
+      </c>
+    </row>
+    <row r="289" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A289">
         <v>288</v>
       </c>
@@ -20260,8 +21131,11 @@
       <c r="S289">
         <v>2.4705882350000001</v>
       </c>
-    </row>
-    <row r="290" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T289">
+        <v>7.8590140485829893E-3</v>
+      </c>
+    </row>
+    <row r="290" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A290">
         <v>289</v>
       </c>
@@ -20316,8 +21190,11 @@
       <c r="S290">
         <v>5</v>
       </c>
-    </row>
-    <row r="291" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T290">
+        <v>2.8340080971659899E-2</v>
+      </c>
+    </row>
+    <row r="291" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A291">
         <v>290</v>
       </c>
@@ -20372,8 +21249,11 @@
       <c r="S291">
         <v>10.5</v>
       </c>
-    </row>
-    <row r="292" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T291">
+        <v>7.28744939271255E-2</v>
+      </c>
+    </row>
+    <row r="292" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A292">
         <v>291</v>
       </c>
@@ -20427,6 +21307,9 @@
       </c>
       <c r="S292">
         <v>9</v>
+      </c>
+      <c r="T292">
+        <v>6.0728744939271197E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20436,14 +21319,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAEBBF30-AA6E-41FB-8FC6-29278057C8E8}">
-  <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.28515625" customWidth="1"/>
-    <col min="2" max="2" width="75.140625" customWidth="1"/>
+    <col min="1" max="1" width="23.26953125" customWidth="1"/>
+    <col min="2" max="2" width="75.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>984</v>
       </c>
@@ -20451,7 +21334,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -20459,7 +21342,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -20467,7 +21350,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>988</v>
       </c>
@@ -20475,7 +21358,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -20483,7 +21366,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -20491,7 +21374,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -20499,7 +21382,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -20507,7 +21390,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -20515,7 +21398,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -20523,7 +21406,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -20531,7 +21414,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -20539,7 +21422,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -20547,7 +21430,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -20555,7 +21438,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -20563,7 +21446,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -20571,7 +21454,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -20579,7 +21462,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -20587,12 +21470,20 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" t="s">
         <v>1004</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1006</v>
       </c>
     </row>
   </sheetData>
